--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="299">
   <si>
     <t/>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>C/B TEH BBK BIRU 80G</t>
+  </si>
+  <si>
+    <t>,(E-3B)</t>
   </si>
   <si>
     <t>10008114</t>
@@ -2564,15 +2567,15 @@
         <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2589,10 +2592,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2609,10 +2612,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2629,10 +2632,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2649,10 +2652,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2669,10 +2672,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2689,10 +2692,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2709,10 +2712,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2729,10 +2732,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2749,10 +2752,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2769,10 +2772,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2789,10 +2792,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2809,10 +2812,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2829,10 +2832,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2849,10 +2852,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2869,10 +2872,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2889,10 +2892,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2904,15 +2907,15 @@
         <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2924,15 +2927,15 @@
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2949,10 +2952,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2964,15 +2967,15 @@
         <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2984,15 +2987,15 @@
         <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3009,10 +3012,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3029,10 +3032,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3049,10 +3052,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3069,10 +3072,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3089,10 +3092,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3109,10 +3112,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3129,10 +3132,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3149,10 +3152,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3169,10 +3172,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3189,10 +3192,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3209,10 +3212,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3229,10 +3232,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3249,10 +3252,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3269,10 +3272,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3289,10 +3292,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3304,15 +3307,15 @@
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3324,15 +3327,15 @@
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3344,15 +3347,15 @@
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3369,10 +3372,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3389,10 +3392,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3409,10 +3412,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3429,10 +3432,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3449,10 +3452,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3469,10 +3472,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3489,10 +3492,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3509,10 +3512,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3529,10 +3532,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3549,10 +3552,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3569,10 +3572,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3589,10 +3592,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3609,10 +3612,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3629,10 +3632,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3649,10 +3652,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3669,10 +3672,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3689,10 +3692,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3709,10 +3712,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3729,10 +3732,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3749,10 +3752,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -3769,10 +3772,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -3789,10 +3792,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -3809,10 +3812,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -3829,10 +3832,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -3849,10 +3852,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -3869,10 +3872,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3889,10 +3892,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3909,10 +3912,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -3929,10 +3932,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -3949,10 +3952,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3969,10 +3972,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -3989,10 +3992,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4009,10 +4012,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4029,10 +4032,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
   <si>
     <t/>
   </si>
@@ -244,12 +244,6 @@
     <t>T/J MADU TJ MRNI 150</t>
   </si>
   <si>
-    <t>20069858</t>
-  </si>
-  <si>
-    <t>T/J MADU KRMA TJ 150</t>
-  </si>
-  <si>
     <t>20073984</t>
   </si>
   <si>
@@ -460,9 +454,6 @@
     <t>C/B TEH BBK BIRU 80G</t>
   </si>
   <si>
-    <t>,(E-3B)</t>
-  </si>
-  <si>
     <t>10008114</t>
   </si>
   <si>
@@ -632,6 +623,12 @@
   </si>
   <si>
     <t>SIMBA CEREAL CKT 72G</t>
+  </si>
+  <si>
+    <t>20142007</t>
+  </si>
+  <si>
+    <t>NSCFE KP KNTL6X39G</t>
   </si>
   <si>
     <t>10025301</t>
@@ -1924,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1944,10 +1941,10 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1964,18 +1961,18 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1984,18 +1981,18 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2004,18 +2001,18 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2024,7 +2021,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -2032,10 +2029,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2044,30 +2041,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,7 +2081,7 @@
         <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -2104,10 +2101,10 @@
         <v>14</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2121,7 @@
         <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>23</v>
@@ -2144,10 +2141,10 @@
         <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2164,10 +2161,10 @@
         <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>23</v>
@@ -2204,7 +2201,7 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>23</v>
@@ -2221,21 +2218,21 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2244,10 +2241,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,10 +2261,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2284,7 +2281,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>23</v>
@@ -2304,7 +2301,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>23</v>
@@ -2324,7 +2321,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>23</v>
@@ -2341,13 +2338,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2364,10 +2361,10 @@
         <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2384,7 +2381,7 @@
         <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>23</v>
@@ -2404,7 +2401,7 @@
         <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -2424,7 +2421,7 @@
         <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -2444,7 +2441,7 @@
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -2461,10 +2458,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -2484,7 +2481,7 @@
         <v>26</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -2504,10 +2501,10 @@
         <v>26</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2524,10 +2521,10 @@
         <v>26</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2544,10 +2541,10 @@
         <v>26</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2564,18 +2561,18 @@
         <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>149</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2584,18 +2581,18 @@
         <v>26</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2604,18 +2601,18 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2624,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2632,10 +2629,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2644,7 +2641,7 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>19</v>
@@ -2652,30 +2649,30 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2684,7 +2681,7 @@
         <v>30</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2692,10 +2689,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2704,7 +2701,7 @@
         <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2712,30 +2709,30 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2744,7 +2741,7 @@
         <v>49</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>19</v>
@@ -2752,10 +2749,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2764,7 +2761,7 @@
         <v>49</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>19</v>
@@ -2772,10 +2769,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2784,18 +2781,18 @@
         <v>49</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2804,18 +2801,18 @@
         <v>49</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2824,18 +2821,18 @@
         <v>49</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2844,18 +2841,18 @@
         <v>49</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2864,7 +2861,7 @@
         <v>49</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>15</v>
@@ -2872,22 +2869,22 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2904,18 +2901,18 @@
         <v>52</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2924,18 +2921,18 @@
         <v>52</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2944,18 +2941,18 @@
         <v>52</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2964,18 +2961,18 @@
         <v>52</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2984,38 +2981,38 @@
         <v>52</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3024,7 +3021,7 @@
         <v>55</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>23</v>
@@ -3032,10 +3029,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3044,7 +3041,7 @@
         <v>55</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -3052,10 +3049,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3064,7 +3061,7 @@
         <v>55</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -3072,10 +3069,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3084,7 +3081,7 @@
         <v>55</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -3092,10 +3089,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3104,18 +3101,18 @@
         <v>55</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3124,18 +3121,18 @@
         <v>55</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3152,10 +3149,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3172,10 +3169,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3192,10 +3189,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3212,10 +3209,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3232,10 +3229,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3252,10 +3249,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3272,10 +3269,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3292,76 +3289,76 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>14</v>
@@ -3372,16 +3369,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>18</v>
@@ -3392,16 +3389,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>22</v>
@@ -3412,16 +3409,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>26</v>
@@ -3432,16 +3429,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>30</v>
@@ -3452,16 +3449,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
@@ -3472,16 +3469,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -3492,16 +3489,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>11</v>
@@ -3512,16 +3509,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>14</v>
@@ -3532,16 +3529,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -3552,16 +3549,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>22</v>
@@ -3572,16 +3569,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>26</v>
@@ -3592,16 +3589,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>30</v>
@@ -3612,16 +3609,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>4</v>
@@ -3632,16 +3629,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -3652,16 +3649,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>11</v>
@@ -3672,16 +3669,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>14</v>
@@ -3692,16 +3689,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>18</v>
@@ -3712,16 +3709,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>22</v>
@@ -3732,16 +3729,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>26</v>
@@ -3752,16 +3749,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>4</v>
@@ -3772,16 +3769,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -3792,16 +3789,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>11</v>
@@ -3812,16 +3809,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>14</v>
@@ -3832,16 +3829,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>18</v>
@@ -3852,16 +3849,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>22</v>
@@ -3872,16 +3869,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>4</v>
@@ -3892,16 +3889,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>8</v>
@@ -3912,16 +3909,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>11</v>
@@ -3932,16 +3929,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>14</v>
@@ -3952,16 +3949,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>18</v>
@@ -3972,16 +3969,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>22</v>
@@ -3992,16 +3989,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>26</v>
@@ -4012,16 +4009,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>30</v>
@@ -4032,16 +4029,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>49</v>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -262,601 +262,601 @@
     <t>MDRASA MADU OR12X20G</t>
   </si>
   <si>
+    <t>20139758</t>
+  </si>
+  <si>
+    <t>MDRASA JH.MRH LMN160</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
-    <t>20139758</t>
-  </si>
-  <si>
-    <t>MDRASA JH.MRH LMN160</t>
+    <t>20140007</t>
+  </si>
+  <si>
+    <t>NSNTARA MD RANDU 100</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>20140007</t>
-  </si>
-  <si>
-    <t>NSNTARA MD RANDU 100</t>
+    <t>20139996</t>
+  </si>
+  <si>
+    <t>NUSANTARA MD RJ 100</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>20139996</t>
-  </si>
-  <si>
-    <t>NUSANTARA MD RJ 100</t>
+    <t>20139997</t>
+  </si>
+  <si>
+    <t>FLORA MADU 250G</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>20139997</t>
-  </si>
-  <si>
-    <t>FLORA MADU 250G</t>
+    <t>10011021</t>
+  </si>
+  <si>
+    <t>SIMBA CRL C/C COK 34</t>
+  </si>
+  <si>
+    <t>10011020</t>
+  </si>
+  <si>
+    <t>SIMBA CRL C/C PTH 34</t>
+  </si>
+  <si>
+    <t>10025006</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO.COMBO 30</t>
+  </si>
+  <si>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL COKLT 30</t>
+  </si>
+  <si>
+    <t>20113150</t>
+  </si>
+  <si>
+    <t>SIMBA CRL CC STRW 34</t>
+  </si>
+  <si>
+    <t>20111959</t>
+  </si>
+  <si>
+    <t>KOKO KRNCH DB.CHO 30</t>
+  </si>
+  <si>
+    <t>20046903</t>
+  </si>
+  <si>
+    <t>NESTLE HONY STAR 30G</t>
+  </si>
+  <si>
+    <t>20136090</t>
+  </si>
+  <si>
+    <t>NESTLE TRIX CUP 30G</t>
+  </si>
+  <si>
+    <t>20137761</t>
+  </si>
+  <si>
+    <t>LARISST CRISPY CHO50</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20137762</t>
+  </si>
+  <si>
+    <t>LARISST CRISPY STR50</t>
+  </si>
+  <si>
+    <t>20132345</t>
+  </si>
+  <si>
+    <t>KELLOG FROT LOOPS 55</t>
+  </si>
+  <si>
+    <t>20071767</t>
+  </si>
+  <si>
+    <t>NESTLE HONY STAR 70G</t>
+  </si>
+  <si>
+    <t>20134846</t>
+  </si>
+  <si>
+    <t>KELLOG GRNL BRRIES40</t>
+  </si>
+  <si>
+    <t>20136091</t>
+  </si>
+  <si>
+    <t>NESTLE TRIX PCK 60G</t>
+  </si>
+  <si>
+    <t>20053733</t>
+  </si>
+  <si>
+    <t>SIMBA C/CHIP COK 150</t>
+  </si>
+  <si>
+    <t>20136567</t>
+  </si>
+  <si>
+    <t>SIMBA MAGIC RNBW 150</t>
+  </si>
+  <si>
+    <t>10036854</t>
+  </si>
+  <si>
+    <t>MILO CEREAL BOX 150G</t>
+  </si>
+  <si>
+    <t>10036861</t>
+  </si>
+  <si>
+    <t>NESTLE HONEY STAR150</t>
+  </si>
+  <si>
+    <t>20138034</t>
+  </si>
+  <si>
+    <t>KLOGGS COCO FILL 150</t>
+  </si>
+  <si>
+    <t>10003828</t>
+  </si>
+  <si>
+    <t>QUAKER REF MERAH 200</t>
+  </si>
+  <si>
+    <t>20139842</t>
+  </si>
+  <si>
+    <t>POCI TEH TRK AREN 5S</t>
+  </si>
+  <si>
+    <t>20140428</t>
+  </si>
+  <si>
+    <t>POCI SK.MTCHA LAT 5S</t>
+  </si>
+  <si>
+    <t>20010085</t>
+  </si>
+  <si>
+    <t>MAX TEA LMN TEA 5X25</t>
+  </si>
+  <si>
+    <t>10004018</t>
+  </si>
+  <si>
+    <t>TONG TJI TEH SUPER80</t>
+  </si>
+  <si>
+    <t>10003061</t>
+  </si>
+  <si>
+    <t>C/B TEH BBK BIRU 80G</t>
+  </si>
+  <si>
+    <t>10008114</t>
+  </si>
+  <si>
+    <t>TONG TJI PREM 10X9GR</t>
+  </si>
+  <si>
+    <t>20114869</t>
+  </si>
+  <si>
+    <t>AMH JAHE MERAH 5'S</t>
+  </si>
+  <si>
+    <t>20039610</t>
+  </si>
+  <si>
+    <t>S/M JAHE SUSU 10X27</t>
+  </si>
+  <si>
+    <t>20120442</t>
+  </si>
+  <si>
+    <t>G/D COKIE N CRM 5'S</t>
+  </si>
+  <si>
+    <t>20097469</t>
+  </si>
+  <si>
+    <t>LUWAK WHT TRK MLK 6S</t>
+  </si>
+  <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 9X20</t>
+  </si>
+  <si>
+    <t>20073043</t>
+  </si>
+  <si>
+    <t>LUWAK WHT LESS 9'S</t>
+  </si>
+  <si>
+    <t>20055300</t>
+  </si>
+  <si>
+    <t>LUWAK WHT 3RASA10X20</t>
+  </si>
+  <si>
+    <t>10000638</t>
+  </si>
+  <si>
+    <t>INDOCAFE MIX 5X20GR</t>
+  </si>
+  <si>
+    <t>10036848</t>
+  </si>
+  <si>
+    <t>INDOCAFE CF.MIX30X20</t>
+  </si>
+  <si>
+    <t>20042025</t>
+  </si>
+  <si>
+    <t>INDOCAFE MX 3IN1 10S</t>
+  </si>
+  <si>
+    <t>20093327</t>
+  </si>
+  <si>
+    <t>TORABIKA CAP PCK 10S</t>
+  </si>
+  <si>
+    <t>20103738</t>
+  </si>
+  <si>
+    <t>FRESCO CAPPUCCINO 9S</t>
+  </si>
+  <si>
+    <t>20054633</t>
+  </si>
+  <si>
+    <t>INDOCAFE CPUCINO 10S</t>
+  </si>
+  <si>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPUCINO 10X25G</t>
+  </si>
+  <si>
+    <t>10003922</t>
+  </si>
+  <si>
+    <t>ABC KP&amp;GULA+SS.10X30</t>
+  </si>
+  <si>
+    <t>20134887</t>
+  </si>
+  <si>
+    <t>TOP GULA AREN 396G</t>
+  </si>
+  <si>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20134965</t>
+  </si>
+  <si>
+    <t>TOP/COFF MKACHNO 198</t>
+  </si>
+  <si>
+    <t>20130895</t>
+  </si>
+  <si>
+    <t>T/C KPI SS GL.ARN 9S</t>
+  </si>
+  <si>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
+  </si>
+  <si>
+    <t>20095226</t>
+  </si>
+  <si>
+    <t>TOP COFF CAPPCNO 6'S</t>
+  </si>
+  <si>
+    <t>20041562</t>
+  </si>
+  <si>
+    <t>TOP COFFEE SUSU 10'S</t>
+  </si>
+  <si>
+    <t>20105103</t>
+  </si>
+  <si>
+    <t>MILO SRBK COKLAT 4'S</t>
+  </si>
+  <si>
+    <t>20103271</t>
+  </si>
+  <si>
+    <t>CHOCODRINK BLG 6'S</t>
+  </si>
+  <si>
+    <t>20131214</t>
+  </si>
+  <si>
+    <t>BENG2 CHOCO DRNK 10S</t>
+  </si>
+  <si>
+    <t>20066440</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO KRNCH 70</t>
+  </si>
+  <si>
+    <t>20134578</t>
+  </si>
+  <si>
+    <t>KELLOGGS COCO FILL60</t>
+  </si>
+  <si>
+    <t>10030665</t>
+  </si>
+  <si>
+    <t>SIMBA CEREAL CKT 72G</t>
+  </si>
+  <si>
+    <t>20142007</t>
+  </si>
+  <si>
+    <t>NSCFE KP KNTL6X39G</t>
+  </si>
+  <si>
+    <t>10025301</t>
+  </si>
+  <si>
+    <t>QUAKER OAT MERAH 800</t>
+  </si>
+  <si>
+    <t>20138019</t>
+  </si>
+  <si>
+    <t>QUAKER 3IN1 MOCHA 8S</t>
+  </si>
+  <si>
+    <t>20001605</t>
+  </si>
+  <si>
+    <t>ENRGEN CKLT PCK 10'S</t>
+  </si>
+  <si>
+    <t>20001604</t>
+  </si>
+  <si>
+    <t>ENRGEN VAN PCK 10'S</t>
+  </si>
+  <si>
+    <t>20001606</t>
+  </si>
+  <si>
+    <t>ENERGEN KCNG.HJ 10'S</t>
+  </si>
+  <si>
+    <t>10036853</t>
+  </si>
+  <si>
+    <t>ENERGEN VNLA BOX 5'S</t>
+  </si>
+  <si>
+    <t>10003340</t>
+  </si>
+  <si>
+    <t>ENRGEN CKLT BOX 5'S</t>
+  </si>
+  <si>
+    <t>20131221</t>
+  </si>
+  <si>
+    <t>CHAMPION COKLAT 10'S</t>
+  </si>
+  <si>
+    <t>20097104</t>
+  </si>
+  <si>
+    <t>NEO/CF MCHNO 6+3X20G</t>
+  </si>
+  <si>
+    <t>20109015</t>
+  </si>
+  <si>
+    <t>NEO/C TRAMSU 6+3X20G</t>
+  </si>
+  <si>
+    <t>20099155</t>
+  </si>
+  <si>
+    <t>NEO/C CRML.MC 6+3X20</t>
+  </si>
+  <si>
+    <t>20125633</t>
+  </si>
+  <si>
+    <t>ABC GL AREN PCK 9'S</t>
+  </si>
+  <si>
+    <t>20098168</t>
+  </si>
+  <si>
+    <t>PIKOPI 3IN1 PCK 9'S</t>
+  </si>
+  <si>
+    <t>20122406</t>
+  </si>
+  <si>
+    <t>PIKOPI GULA AREN 6+3</t>
+  </si>
+  <si>
+    <t>10006712</t>
+  </si>
+  <si>
+    <t>K/API KOPI SUSU10X31</t>
+  </si>
+  <si>
+    <t>20119091</t>
+  </si>
+  <si>
+    <t>K/A GL.AREN SM 10'S</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060370</t>
+  </si>
+  <si>
+    <t>G/DAY CHOCOCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060371</t>
+  </si>
+  <si>
+    <t>G/DAY VNL.LATTE 10'S</t>
+  </si>
+  <si>
+    <t>20100796</t>
+  </si>
+  <si>
+    <t>TORABIKA CRMY.LAT10S</t>
+  </si>
+  <si>
+    <t>20138571</t>
+  </si>
+  <si>
+    <t>G/DAY LATTE ORI 10S</t>
+  </si>
+  <si>
+    <t>20138948</t>
+  </si>
+  <si>
+    <t>G/DAY BTRSCOTCH 10S</t>
+  </si>
+  <si>
+    <t>20023287</t>
+  </si>
+  <si>
+    <t>K/API MANTAP 8X24GR</t>
+  </si>
+  <si>
+    <t>20138370</t>
+  </si>
+  <si>
+    <t>GDJAH SPC MIX PCK 10</t>
+  </si>
+  <si>
+    <t>20131377</t>
+  </si>
+  <si>
+    <t>KPL API ONE+GULA 10S</t>
+  </si>
+  <si>
+    <t>20112372</t>
+  </si>
+  <si>
+    <t>GADJAH KP.TUBRUK 10S</t>
+  </si>
+  <si>
+    <t>20125856</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN 100G</t>
+  </si>
+  <si>
+    <t>20055977</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN50+50G</t>
+  </si>
+  <si>
+    <t>20067868</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 5'S</t>
+  </si>
+  <si>
+    <t>20043807</t>
+  </si>
+  <si>
+    <t>FRESCO KOPI+GULA 8S</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
+  </si>
+  <si>
+    <t>10003873</t>
+  </si>
+  <si>
+    <t>K/API KOPI BUBUK 350</t>
+  </si>
+  <si>
+    <t>20098227</t>
+  </si>
+  <si>
+    <t>K/API KP.BBK SPC 350</t>
+  </si>
+  <si>
+    <t>20140181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPCL 250G</t>
+  </si>
+  <si>
+    <t>20086181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPC 20X6G</t>
+  </si>
+  <si>
+    <t>20002725</t>
+  </si>
+  <si>
+    <t>KPL API SPC.MIX 20'S</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>10000345</t>
+  </si>
+  <si>
+    <t>NESCAFE CLASSIC 100G</t>
   </si>
   <si>
     <t>17</t>
-  </si>
-  <si>
-    <t>10011021</t>
-  </si>
-  <si>
-    <t>SIMBA CRL C/C COK 34</t>
-  </si>
-  <si>
-    <t>10011020</t>
-  </si>
-  <si>
-    <t>SIMBA CRL C/C PTH 34</t>
-  </si>
-  <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO.COMBO 30</t>
-  </si>
-  <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL COKLT 30</t>
-  </si>
-  <si>
-    <t>20113150</t>
-  </si>
-  <si>
-    <t>SIMBA CRL CC STRW 34</t>
-  </si>
-  <si>
-    <t>20111959</t>
-  </si>
-  <si>
-    <t>KOKO KRNCH DB.CHO 30</t>
-  </si>
-  <si>
-    <t>20046903</t>
-  </si>
-  <si>
-    <t>NESTLE HONY STAR 30G</t>
-  </si>
-  <si>
-    <t>20136090</t>
-  </si>
-  <si>
-    <t>NESTLE TRIX CUP 30G</t>
-  </si>
-  <si>
-    <t>20137761</t>
-  </si>
-  <si>
-    <t>LARISST CRISPY CHO50</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20137762</t>
-  </si>
-  <si>
-    <t>LARISST CRISPY STR50</t>
-  </si>
-  <si>
-    <t>20132345</t>
-  </si>
-  <si>
-    <t>KELLOG FROT LOOPS 55</t>
-  </si>
-  <si>
-    <t>20071767</t>
-  </si>
-  <si>
-    <t>NESTLE HONY STAR 70G</t>
-  </si>
-  <si>
-    <t>20134846</t>
-  </si>
-  <si>
-    <t>KELLOG GRNL BRRIES40</t>
-  </si>
-  <si>
-    <t>20136091</t>
-  </si>
-  <si>
-    <t>NESTLE TRIX PCK 60G</t>
-  </si>
-  <si>
-    <t>20053733</t>
-  </si>
-  <si>
-    <t>SIMBA C/CHIP COK 150</t>
-  </si>
-  <si>
-    <t>20136567</t>
-  </si>
-  <si>
-    <t>SIMBA MAGIC RNBW 150</t>
-  </si>
-  <si>
-    <t>10036854</t>
-  </si>
-  <si>
-    <t>MILO CEREAL BOX 150G</t>
-  </si>
-  <si>
-    <t>10036861</t>
-  </si>
-  <si>
-    <t>NESTLE HONEY STAR150</t>
-  </si>
-  <si>
-    <t>20138034</t>
-  </si>
-  <si>
-    <t>KLOGGS COCO FILL 150</t>
-  </si>
-  <si>
-    <t>10003828</t>
-  </si>
-  <si>
-    <t>QUAKER REF MERAH 200</t>
-  </si>
-  <si>
-    <t>20139842</t>
-  </si>
-  <si>
-    <t>POCI TEH TRK AREN 5S</t>
-  </si>
-  <si>
-    <t>20140428</t>
-  </si>
-  <si>
-    <t>POCI SK.MTCHA LAT 5S</t>
-  </si>
-  <si>
-    <t>20010085</t>
-  </si>
-  <si>
-    <t>MAX TEA LMN TEA 5X25</t>
-  </si>
-  <si>
-    <t>10004018</t>
-  </si>
-  <si>
-    <t>TONG TJI TEH SUPER80</t>
-  </si>
-  <si>
-    <t>10003061</t>
-  </si>
-  <si>
-    <t>C/B TEH BBK BIRU 80G</t>
-  </si>
-  <si>
-    <t>10008114</t>
-  </si>
-  <si>
-    <t>TONG TJI PREM 10X9GR</t>
-  </si>
-  <si>
-    <t>20114869</t>
-  </si>
-  <si>
-    <t>AMH JAHE MERAH 5'S</t>
-  </si>
-  <si>
-    <t>20039610</t>
-  </si>
-  <si>
-    <t>S/M JAHE SUSU 10X27</t>
-  </si>
-  <si>
-    <t>20120442</t>
-  </si>
-  <si>
-    <t>G/D COKIE N CRM 5'S</t>
-  </si>
-  <si>
-    <t>20097469</t>
-  </si>
-  <si>
-    <t>LUWAK WHT TRK MLK 6S</t>
-  </si>
-  <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 9X20</t>
-  </si>
-  <si>
-    <t>20073043</t>
-  </si>
-  <si>
-    <t>LUWAK WHT LESS 9'S</t>
-  </si>
-  <si>
-    <t>20055300</t>
-  </si>
-  <si>
-    <t>LUWAK WHT 3RASA10X20</t>
-  </si>
-  <si>
-    <t>10000638</t>
-  </si>
-  <si>
-    <t>INDOCAFE MIX 5X20GR</t>
-  </si>
-  <si>
-    <t>10036848</t>
-  </si>
-  <si>
-    <t>INDOCAFE CF.MIX30X20</t>
-  </si>
-  <si>
-    <t>20042025</t>
-  </si>
-  <si>
-    <t>INDOCAFE MX 3IN1 10S</t>
-  </si>
-  <si>
-    <t>20093327</t>
-  </si>
-  <si>
-    <t>TORABIKA CAP PCK 10S</t>
-  </si>
-  <si>
-    <t>20103738</t>
-  </si>
-  <si>
-    <t>FRESCO CAPPUCCINO 9S</t>
-  </si>
-  <si>
-    <t>20054633</t>
-  </si>
-  <si>
-    <t>INDOCAFE CPUCINO 10S</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPUCINO 10X25G</t>
-  </si>
-  <si>
-    <t>10003922</t>
-  </si>
-  <si>
-    <t>ABC KP&amp;GULA+SS.10X30</t>
-  </si>
-  <si>
-    <t>20134887</t>
-  </si>
-  <si>
-    <t>TOP GULA AREN 396G</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20134965</t>
-  </si>
-  <si>
-    <t>TOP/COFF MKACHNO 198</t>
-  </si>
-  <si>
-    <t>20130895</t>
-  </si>
-  <si>
-    <t>T/C KPI SS GL.ARN 9S</t>
-  </si>
-  <si>
-    <t>20107729</t>
-  </si>
-  <si>
-    <t>TOP COFF GL AREN 9'S</t>
-  </si>
-  <si>
-    <t>20095226</t>
-  </si>
-  <si>
-    <t>TOP COFF CAPPCNO 6'S</t>
-  </si>
-  <si>
-    <t>20041562</t>
-  </si>
-  <si>
-    <t>TOP COFFEE SUSU 10'S</t>
-  </si>
-  <si>
-    <t>20105103</t>
-  </si>
-  <si>
-    <t>MILO SRBK COKLAT 4'S</t>
-  </si>
-  <si>
-    <t>20103271</t>
-  </si>
-  <si>
-    <t>CHOCODRINK BLG 6'S</t>
-  </si>
-  <si>
-    <t>20131214</t>
-  </si>
-  <si>
-    <t>BENG2 CHOCO DRNK 10S</t>
-  </si>
-  <si>
-    <t>20066440</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO KRNCH 70</t>
-  </si>
-  <si>
-    <t>20134578</t>
-  </si>
-  <si>
-    <t>KELLOGGS COCO FILL60</t>
-  </si>
-  <si>
-    <t>10030665</t>
-  </si>
-  <si>
-    <t>SIMBA CEREAL CKT 72G</t>
-  </si>
-  <si>
-    <t>20142007</t>
-  </si>
-  <si>
-    <t>NSCFE KP KNTL6X39G</t>
-  </si>
-  <si>
-    <t>10025301</t>
-  </si>
-  <si>
-    <t>QUAKER OAT MERAH 800</t>
-  </si>
-  <si>
-    <t>20138019</t>
-  </si>
-  <si>
-    <t>QUAKER 3IN1 MOCHA 8S</t>
-  </si>
-  <si>
-    <t>20001605</t>
-  </si>
-  <si>
-    <t>ENRGEN CKLT PCK 10'S</t>
-  </si>
-  <si>
-    <t>20001604</t>
-  </si>
-  <si>
-    <t>ENRGEN VAN PCK 10'S</t>
-  </si>
-  <si>
-    <t>20001606</t>
-  </si>
-  <si>
-    <t>ENERGEN KCNG.HJ 10'S</t>
-  </si>
-  <si>
-    <t>10036853</t>
-  </si>
-  <si>
-    <t>ENERGEN VNLA BOX 5'S</t>
-  </si>
-  <si>
-    <t>10003340</t>
-  </si>
-  <si>
-    <t>ENRGEN CKLT BOX 5'S</t>
-  </si>
-  <si>
-    <t>20131221</t>
-  </si>
-  <si>
-    <t>CHAMPION COKLAT 10'S</t>
-  </si>
-  <si>
-    <t>20097104</t>
-  </si>
-  <si>
-    <t>NEO/CF MCHNO 6+3X20G</t>
-  </si>
-  <si>
-    <t>20109015</t>
-  </si>
-  <si>
-    <t>NEO/C TRAMSU 6+3X20G</t>
-  </si>
-  <si>
-    <t>20099155</t>
-  </si>
-  <si>
-    <t>NEO/C CRML.MC 6+3X20</t>
-  </si>
-  <si>
-    <t>20125633</t>
-  </si>
-  <si>
-    <t>ABC GL AREN PCK 9'S</t>
-  </si>
-  <si>
-    <t>20098168</t>
-  </si>
-  <si>
-    <t>PIKOPI 3IN1 PCK 9'S</t>
-  </si>
-  <si>
-    <t>20122406</t>
-  </si>
-  <si>
-    <t>PIKOPI GULA AREN 6+3</t>
-  </si>
-  <si>
-    <t>10006712</t>
-  </si>
-  <si>
-    <t>K/API KOPI SUSU10X31</t>
-  </si>
-  <si>
-    <t>20119091</t>
-  </si>
-  <si>
-    <t>K/A GL.AREN SM 10'S</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060370</t>
-  </si>
-  <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060371</t>
-  </si>
-  <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
-  </si>
-  <si>
-    <t>20100796</t>
-  </si>
-  <si>
-    <t>TORABIKA CRMY.LAT10S</t>
-  </si>
-  <si>
-    <t>20138571</t>
-  </si>
-  <si>
-    <t>G/DAY LATTE ORI 10S</t>
-  </si>
-  <si>
-    <t>20138948</t>
-  </si>
-  <si>
-    <t>G/DAY BTRSCOTCH 10S</t>
-  </si>
-  <si>
-    <t>20023287</t>
-  </si>
-  <si>
-    <t>K/API MANTAP 8X24GR</t>
-  </si>
-  <si>
-    <t>20138370</t>
-  </si>
-  <si>
-    <t>GDJAH SPC MIX PCK 10</t>
-  </si>
-  <si>
-    <t>20131377</t>
-  </si>
-  <si>
-    <t>KPL API ONE+GULA 10S</t>
-  </si>
-  <si>
-    <t>20112372</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 10S</t>
-  </si>
-  <si>
-    <t>20125856</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN 100G</t>
-  </si>
-  <si>
-    <t>20055977</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN50+50G</t>
-  </si>
-  <si>
-    <t>20067868</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 5'S</t>
-  </si>
-  <si>
-    <t>20043807</t>
-  </si>
-  <si>
-    <t>FRESCO KOPI+GULA 8S</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>10003873</t>
-  </si>
-  <si>
-    <t>K/API KOPI BUBUK 350</t>
-  </si>
-  <si>
-    <t>20098227</t>
-  </si>
-  <si>
-    <t>K/API KP.BBK SPC 350</t>
-  </si>
-  <si>
-    <t>20140181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPCL 250G</t>
-  </si>
-  <si>
-    <t>20086181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPC 20X6G</t>
-  </si>
-  <si>
-    <t>20002725</t>
-  </si>
-  <si>
-    <t>KPL API SPC.MIX 20'S</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
-    <t>10000345</t>
-  </si>
-  <si>
-    <t>NESCAFE CLASSIC 100G</t>
   </si>
   <si>
     <t>20129093</t>
@@ -1921,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1941,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1961,7 +1961,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>15</v>
@@ -1969,10 +1969,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1981,7 +1981,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>23</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2001,7 +2001,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -2009,10 +2009,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2021,7 +2021,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2041,7 +2041,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>23</v>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2129,10 +2129,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2224,15 +2224,15 @@
         <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2244,15 +2244,15 @@
         <v>8</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2369,10 +2369,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -2884,15 +2884,15 @@
         <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2904,15 +2904,15 @@
         <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -2944,15 +2944,15 @@
         <v>14</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -2964,15 +2964,15 @@
         <v>18</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3049,10 +3049,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3089,10 +3089,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3229,10 +3229,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3269,10 +3269,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3289,76 +3289,76 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>14</v>
@@ -3369,16 +3369,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>18</v>
@@ -3389,16 +3389,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>22</v>
@@ -3409,16 +3409,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>26</v>
@@ -3429,16 +3429,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>30</v>
@@ -3449,16 +3449,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
@@ -3469,16 +3469,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -3489,16 +3489,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>11</v>
@@ -3509,16 +3509,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>14</v>
@@ -3529,16 +3529,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -3549,16 +3549,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>22</v>
@@ -3569,16 +3569,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>26</v>
@@ -3589,16 +3589,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>30</v>
@@ -3609,16 +3609,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>4</v>
@@ -3629,16 +3629,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -3649,16 +3649,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>11</v>
@@ -3669,16 +3669,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>14</v>
@@ -3689,16 +3689,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>18</v>
@@ -3709,16 +3709,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>22</v>
@@ -3729,16 +3729,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>26</v>
@@ -3749,16 +3749,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>4</v>
@@ -3769,16 +3769,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -3789,16 +3789,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>11</v>
@@ -3809,16 +3809,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>14</v>
@@ -3829,16 +3829,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>18</v>
@@ -3849,16 +3849,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>22</v>
@@ -3869,16 +3869,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>4</v>
@@ -3898,7 +3898,7 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>8</v>
@@ -3918,7 +3918,7 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>11</v>
@@ -3938,7 +3938,7 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>14</v>
@@ -3958,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>18</v>
@@ -3978,7 +3978,7 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>22</v>
@@ -3998,7 +3998,7 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>26</v>
@@ -4018,7 +4018,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>30</v>
@@ -4038,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>49</v>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="300">
   <si>
     <t/>
   </si>
@@ -190,6 +190,15 @@
     <t>12</t>
   </si>
   <si>
+    <t>10005797</t>
+  </si>
+  <si>
+    <t>M/R SLIMMING TEA 15S</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>20137476</t>
   </si>
   <si>
@@ -266,9 +275,6 @@
   </si>
   <si>
     <t>MDRASA JH.MRH LMN160</t>
-  </si>
-  <si>
-    <t>13</t>
   </si>
   <si>
     <t>20140007</t>
@@ -1297,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1738,21 +1744,21 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1761,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1769,10 +1775,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1781,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1789,10 +1795,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1801,18 +1807,18 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1821,18 +1827,18 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1841,7 +1847,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1849,10 +1855,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1861,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1869,10 +1875,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1881,18 +1887,18 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1901,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>15</v>
@@ -1909,10 +1915,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1921,7 +1927,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1929,10 +1935,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1941,18 +1947,18 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1961,18 +1967,18 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1981,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2001,18 +2007,18 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2021,7 +2027,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -2029,10 +2035,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2041,30 +2047,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,7 +2087,7 @@
         <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -2101,10 +2107,10 @@
         <v>14</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2121,7 +2127,7 @@
         <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>23</v>
@@ -2141,10 +2147,10 @@
         <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2161,10 +2167,10 @@
         <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2181,7 +2187,7 @@
         <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>23</v>
@@ -2201,7 +2207,7 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>23</v>
@@ -2218,21 +2224,21 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>113</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2241,10 +2247,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2261,10 +2267,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2281,7 +2287,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>23</v>
@@ -2301,7 +2307,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>23</v>
@@ -2321,7 +2327,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>23</v>
@@ -2338,13 +2344,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2361,10 +2367,10 @@
         <v>22</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2381,7 +2387,7 @@
         <v>22</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>23</v>
@@ -2401,7 +2407,7 @@
         <v>22</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -2421,7 +2427,7 @@
         <v>22</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>23</v>
@@ -2441,7 +2447,7 @@
         <v>22</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>23</v>
@@ -2458,10 +2464,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>23</v>
@@ -2481,7 +2487,7 @@
         <v>26</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>23</v>
@@ -2501,10 +2507,10 @@
         <v>26</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2521,10 +2527,10 @@
         <v>26</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2541,10 +2547,10 @@
         <v>26</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2561,10 +2567,10 @@
         <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2581,10 +2587,10 @@
         <v>26</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2601,10 +2607,10 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2621,7 +2627,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2641,7 +2647,7 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>19</v>
@@ -2658,13 +2664,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2681,7 +2687,7 @@
         <v>30</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>5</v>
@@ -2701,7 +2707,7 @@
         <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2718,13 +2724,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2741,7 +2747,7 @@
         <v>49</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>19</v>
@@ -2761,7 +2767,7 @@
         <v>49</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>19</v>
@@ -2781,10 +2787,10 @@
         <v>49</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,10 +2807,10 @@
         <v>49</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2821,10 +2827,10 @@
         <v>49</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2841,10 +2847,10 @@
         <v>49</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2861,7 +2867,7 @@
         <v>49</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>15</v>
@@ -2878,21 +2884,21 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -2901,10 +2907,10 @@
         <v>52</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2921,10 +2927,10 @@
         <v>52</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>15</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2941,10 +2947,10 @@
         <v>52</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,10 +2967,10 @@
         <v>52</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,10 +2987,10 @@
         <v>52</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>15</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2998,13 +3004,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,7 +3027,7 @@
         <v>55</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>23</v>
@@ -3041,7 +3047,7 @@
         <v>55</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -3061,7 +3067,7 @@
         <v>55</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -3081,7 +3087,7 @@
         <v>55</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -3101,10 +3107,10 @@
         <v>55</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3121,10 +3127,10 @@
         <v>55</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3138,10 +3144,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>23</v>
@@ -3161,7 +3167,7 @@
         <v>58</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>23</v>
@@ -3181,7 +3187,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -3201,7 +3207,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -3221,7 +3227,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -3241,7 +3247,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -3261,7 +3267,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -3281,7 +3287,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3298,13 +3304,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>180</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,13 +3324,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,13 +3344,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,13 +3364,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,13 +3384,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,10 +3404,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3418,13 +3424,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,10 +3444,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>15</v>
@@ -3458,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>15</v>
@@ -3478,13 +3484,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3498,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3518,13 +3524,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3558,10 +3564,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -3578,13 +3584,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,13 +3604,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,10 +3624,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3638,10 +3644,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -3658,13 +3664,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3678,13 +3684,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3698,13 +3704,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,13 +3724,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,10 +3744,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -3758,10 +3764,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -3778,10 +3784,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>15</v>
@@ -3798,13 +3804,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3818,13 +3824,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3838,10 +3844,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -3858,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>15</v>
@@ -3878,33 +3884,33 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>96</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,10 +3924,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -3938,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3958,10 +3964,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3978,10 +3984,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -3998,13 +4004,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4018,10 +4024,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>15</v>
@@ -4038,12 +4044,32 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F138" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
   <si>
     <t/>
   </si>
@@ -638,12 +638,6 @@
   </si>
   <si>
     <t>QUAKER OAT MERAH 800</t>
-  </si>
-  <si>
-    <t>20138019</t>
-  </si>
-  <si>
-    <t>QUAKER 3IN1 MOCHA 8S</t>
   </si>
   <si>
     <t>20001605</t>
@@ -1303,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3187,7 +3181,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -3207,7 +3201,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -3227,7 +3221,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -3247,7 +3241,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -3267,7 +3261,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -3287,7 +3281,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3304,13 +3298,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3327,7 +3321,7 @@
         <v>61</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>182</v>
@@ -3347,7 +3341,7 @@
         <v>61</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>182</v>
@@ -3367,10 +3361,10 @@
         <v>61</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3387,10 +3381,10 @@
         <v>61</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3407,7 +3401,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3427,10 +3421,10 @@
         <v>61</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3447,7 +3441,7 @@
         <v>61</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>15</v>
@@ -3464,10 +3458,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>15</v>
@@ -3487,10 +3481,10 @@
         <v>90</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3507,7 +3501,7 @@
         <v>90</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3527,10 +3521,10 @@
         <v>90</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3547,7 +3541,7 @@
         <v>90</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3567,7 +3561,7 @@
         <v>90</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -3587,10 +3581,10 @@
         <v>90</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3607,10 +3601,10 @@
         <v>90</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3624,10 +3618,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3647,7 +3641,7 @@
         <v>93</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -3667,10 +3661,10 @@
         <v>93</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3687,10 +3681,10 @@
         <v>93</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3707,10 +3701,10 @@
         <v>93</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3727,10 +3721,10 @@
         <v>93</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3747,7 +3741,7 @@
         <v>93</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -3764,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -3787,7 +3781,7 @@
         <v>96</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>15</v>
@@ -3807,10 +3801,10 @@
         <v>96</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3827,10 +3821,10 @@
         <v>96</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3847,7 +3841,7 @@
         <v>96</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -3867,7 +3861,7 @@
         <v>96</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>15</v>
@@ -3884,33 +3878,33 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>96</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,10 +3918,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>23</v>
@@ -3944,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3964,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3984,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>23</v>
@@ -4004,13 +3998,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4024,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>15</v>
@@ -4044,32 +4038,12 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F138" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -628,265 +628,265 @@
     <t>SIMBA CEREAL CKT 72G</t>
   </si>
   <si>
+    <t>20112371</t>
+  </si>
+  <si>
+    <t>GADJAH KP.TUBRUK 138</t>
+  </si>
+  <si>
+    <t>10025301</t>
+  </si>
+  <si>
+    <t>QUAKER OAT MERAH 800</t>
+  </si>
+  <si>
+    <t>20001605</t>
+  </si>
+  <si>
+    <t>ENRGEN CKLT PCK 10'S</t>
+  </si>
+  <si>
+    <t>20001604</t>
+  </si>
+  <si>
+    <t>ENRGEN VAN PCK 10'S</t>
+  </si>
+  <si>
+    <t>20001606</t>
+  </si>
+  <si>
+    <t>ENERGEN KCNG.HJ 10'S</t>
+  </si>
+  <si>
+    <t>10036853</t>
+  </si>
+  <si>
+    <t>ENERGEN VNLA BOX 5'S</t>
+  </si>
+  <si>
+    <t>10003340</t>
+  </si>
+  <si>
+    <t>ENRGEN CKLT BOX 5'S</t>
+  </si>
+  <si>
+    <t>20131221</t>
+  </si>
+  <si>
+    <t>CHAMPION COKLAT 10'S</t>
+  </si>
+  <si>
+    <t>20097104</t>
+  </si>
+  <si>
+    <t>NEO/CF MCHNO 6+3X20G</t>
+  </si>
+  <si>
+    <t>20109015</t>
+  </si>
+  <si>
+    <t>NEO/C TRAMSU 6+3X20G</t>
+  </si>
+  <si>
+    <t>20099155</t>
+  </si>
+  <si>
+    <t>NEO/C CRML.MC 6+3X20</t>
+  </si>
+  <si>
+    <t>20125633</t>
+  </si>
+  <si>
+    <t>ABC GL AREN PCK 9'S</t>
+  </si>
+  <si>
+    <t>20098168</t>
+  </si>
+  <si>
+    <t>PIKOPI 3IN1 PCK 9'S</t>
+  </si>
+  <si>
+    <t>20122406</t>
+  </si>
+  <si>
+    <t>PIKOPI GULA AREN 6+3</t>
+  </si>
+  <si>
+    <t>10006712</t>
+  </si>
+  <si>
+    <t>K/API KOPI SUSU10X31</t>
+  </si>
+  <si>
+    <t>20119091</t>
+  </si>
+  <si>
+    <t>K/A GL.AREN SM 10'S</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060370</t>
+  </si>
+  <si>
+    <t>G/DAY CHOCOCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060371</t>
+  </si>
+  <si>
+    <t>G/DAY VNL.LATTE 10'S</t>
+  </si>
+  <si>
+    <t>20100796</t>
+  </si>
+  <si>
+    <t>TORABIKA CRMY.LAT10S</t>
+  </si>
+  <si>
+    <t>20138571</t>
+  </si>
+  <si>
+    <t>G/DAY LATTE ORI 10S</t>
+  </si>
+  <si>
+    <t>20138948</t>
+  </si>
+  <si>
+    <t>G/DAY BTRSCOTCH 10S</t>
+  </si>
+  <si>
+    <t>20023287</t>
+  </si>
+  <si>
+    <t>K/API MANTAP 8X24GR</t>
+  </si>
+  <si>
+    <t>20138370</t>
+  </si>
+  <si>
+    <t>GDJAH SPC MIX PCK 10</t>
+  </si>
+  <si>
+    <t>20131377</t>
+  </si>
+  <si>
+    <t>KPL API ONE+GULA 10S</t>
+  </si>
+  <si>
+    <t>20112372</t>
+  </si>
+  <si>
+    <t>GADJAH KP.TUBRUK 10S</t>
+  </si>
+  <si>
+    <t>20125856</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN 100G</t>
+  </si>
+  <si>
+    <t>20055977</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI MRN50+50G</t>
+  </si>
+  <si>
+    <t>20067868</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 5'S</t>
+  </si>
+  <si>
+    <t>20043807</t>
+  </si>
+  <si>
+    <t>FRESCO KOPI+GULA 8S</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
+  </si>
+  <si>
+    <t>10003873</t>
+  </si>
+  <si>
+    <t>K/API KOPI BUBUK 350</t>
+  </si>
+  <si>
+    <t>20098227</t>
+  </si>
+  <si>
+    <t>K/API KP.BBK SPC 350</t>
+  </si>
+  <si>
+    <t>20140181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPCL 250G</t>
+  </si>
+  <si>
+    <t>20086181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPC 20X6G</t>
+  </si>
+  <si>
+    <t>20002725</t>
+  </si>
+  <si>
+    <t>KPL API SPC.MIX 20'S</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
+  </si>
+  <si>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20142007</t>
   </si>
   <si>
     <t>NSCFE KP KNTL6X39G</t>
   </si>
   <si>
-    <t>10025301</t>
-  </si>
-  <si>
-    <t>QUAKER OAT MERAH 800</t>
-  </si>
-  <si>
-    <t>20001605</t>
-  </si>
-  <si>
-    <t>ENRGEN CKLT PCK 10'S</t>
-  </si>
-  <si>
-    <t>20001604</t>
-  </si>
-  <si>
-    <t>ENRGEN VAN PCK 10'S</t>
-  </si>
-  <si>
-    <t>20001606</t>
-  </si>
-  <si>
-    <t>ENERGEN KCNG.HJ 10'S</t>
-  </si>
-  <si>
-    <t>10036853</t>
-  </si>
-  <si>
-    <t>ENERGEN VNLA BOX 5'S</t>
-  </si>
-  <si>
-    <t>10003340</t>
-  </si>
-  <si>
-    <t>ENRGEN CKLT BOX 5'S</t>
-  </si>
-  <si>
-    <t>20131221</t>
-  </si>
-  <si>
-    <t>CHAMPION COKLAT 10'S</t>
-  </si>
-  <si>
-    <t>20097104</t>
-  </si>
-  <si>
-    <t>NEO/CF MCHNO 6+3X20G</t>
-  </si>
-  <si>
-    <t>20109015</t>
-  </si>
-  <si>
-    <t>NEO/C TRAMSU 6+3X20G</t>
-  </si>
-  <si>
-    <t>20099155</t>
-  </si>
-  <si>
-    <t>NEO/C CRML.MC 6+3X20</t>
-  </si>
-  <si>
-    <t>20125633</t>
-  </si>
-  <si>
-    <t>ABC GL AREN PCK 9'S</t>
-  </si>
-  <si>
-    <t>20098168</t>
-  </si>
-  <si>
-    <t>PIKOPI 3IN1 PCK 9'S</t>
-  </si>
-  <si>
-    <t>20122406</t>
-  </si>
-  <si>
-    <t>PIKOPI GULA AREN 6+3</t>
-  </si>
-  <si>
-    <t>10006712</t>
-  </si>
-  <si>
-    <t>K/API KOPI SUSU10X31</t>
-  </si>
-  <si>
-    <t>20119091</t>
-  </si>
-  <si>
-    <t>K/A GL.AREN SM 10'S</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060370</t>
-  </si>
-  <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060371</t>
-  </si>
-  <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
-  </si>
-  <si>
-    <t>20100796</t>
-  </si>
-  <si>
-    <t>TORABIKA CRMY.LAT10S</t>
-  </si>
-  <si>
-    <t>20138571</t>
-  </si>
-  <si>
-    <t>G/DAY LATTE ORI 10S</t>
-  </si>
-  <si>
-    <t>20138948</t>
-  </si>
-  <si>
-    <t>G/DAY BTRSCOTCH 10S</t>
-  </si>
-  <si>
-    <t>20023287</t>
-  </si>
-  <si>
-    <t>K/API MANTAP 8X24GR</t>
-  </si>
-  <si>
-    <t>20138370</t>
-  </si>
-  <si>
-    <t>GDJAH SPC MIX PCK 10</t>
-  </si>
-  <si>
-    <t>20131377</t>
-  </si>
-  <si>
-    <t>KPL API ONE+GULA 10S</t>
-  </si>
-  <si>
-    <t>20112372</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 10S</t>
-  </si>
-  <si>
-    <t>20125856</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN 100G</t>
-  </si>
-  <si>
-    <t>20055977</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI MRN50+50G</t>
-  </si>
-  <si>
-    <t>20067868</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 5'S</t>
-  </si>
-  <si>
-    <t>20043807</t>
-  </si>
-  <si>
-    <t>FRESCO KOPI+GULA 8S</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>10003873</t>
-  </si>
-  <si>
-    <t>K/API KOPI BUBUK 350</t>
-  </si>
-  <si>
-    <t>20098227</t>
-  </si>
-  <si>
-    <t>K/API KP.BBK SPC 350</t>
-  </si>
-  <si>
-    <t>20140181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPCL 250G</t>
-  </si>
-  <si>
-    <t>20086181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPC 20X6G</t>
-  </si>
-  <si>
-    <t>20002725</t>
-  </si>
-  <si>
-    <t>KPL API SPC.MIX 20'S</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
-  </si>
-  <si>
     <t>10000345</t>
   </si>
   <si>
     <t>NESCAFE CLASSIC 100G</t>
   </si>
   <si>
-    <t>17</t>
+    <t>20017575</t>
+  </si>
+  <si>
+    <t>NESCAFE CLSC 10X2G</t>
+  </si>
+  <si>
+    <t>10005302</t>
+  </si>
+  <si>
+    <t>NESCAFE CLASIC EKO45</t>
   </si>
   <si>
     <t>20129093</t>
   </si>
   <si>
     <t>GADJAH KP.TUBRUK 60G</t>
-  </si>
-  <si>
-    <t>20112371</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 138</t>
-  </si>
-  <si>
-    <t>20017575</t>
-  </si>
-  <si>
-    <t>NESCAFE CLSC 10X2G</t>
-  </si>
-  <si>
-    <t>20136451</t>
-  </si>
-  <si>
-    <t>NSCAFE AMERICANO 10S</t>
-  </si>
-  <si>
-    <t>10005302</t>
-  </si>
-  <si>
-    <t>NESCAFE CLASIC EKO45</t>
   </si>
   <si>
     <t>10000304</t>
@@ -3884,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="296">
   <si>
     <t/>
   </si>
@@ -319,13 +319,13 @@
     <t>10025006</t>
   </si>
   <si>
-    <t>NESTLE KOKO.COMBO 30</t>
+    <t>NSTL KOKO COMBO 30 G</t>
   </si>
   <si>
     <t>20032723</t>
   </si>
   <si>
-    <t>MILO CEREAL COKLT 30</t>
+    <t>MILO CRL CKLT 30 G</t>
   </si>
   <si>
     <t>20113150</t>
@@ -337,13 +337,13 @@
     <t>20111959</t>
   </si>
   <si>
-    <t>KOKO KRNCH DB.CHO 30</t>
+    <t>NSTL KOKO D CHO 30 G</t>
   </si>
   <si>
     <t>20046903</t>
   </si>
   <si>
-    <t>NESTLE HONY STAR 30G</t>
+    <t>NSTL HONY STAR 30 G</t>
   </si>
   <si>
     <t>20136090</t>
@@ -490,13 +490,13 @@
     <t>20036590</t>
   </si>
   <si>
-    <t>LUWAK WHT ORGL 9X20</t>
+    <t>LWK WHKO ORG 9x20 G</t>
   </si>
   <si>
     <t>20073043</t>
   </si>
   <si>
-    <t>LUWAK WHT LESS 9'S</t>
+    <t>LWK WHKO LS 9x19 G</t>
   </si>
   <si>
     <t>20055300</t>
@@ -718,12 +718,6 @@
     <t>K/API KOPI SUSU10X31</t>
   </si>
   <si>
-    <t>20119091</t>
-  </si>
-  <si>
-    <t>K/A GL.AREN SM 10'S</t>
-  </si>
-  <si>
     <t>20046081</t>
   </si>
   <si>
@@ -811,7 +805,7 @@
     <t>10038932</t>
   </si>
   <si>
-    <t>KPL API SPC MIX 10'S</t>
+    <t>KAPAPI S MIX 10x23 G</t>
   </si>
   <si>
     <t>10003873</t>
@@ -1297,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3438,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>15</v>
@@ -3461,10 +3455,10 @@
         <v>90</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,7 +3475,7 @@
         <v>90</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3501,10 +3495,10 @@
         <v>90</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3521,7 +3515,7 @@
         <v>90</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -3541,7 +3535,7 @@
         <v>90</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3561,10 +3555,10 @@
         <v>90</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,10 +3575,10 @@
         <v>90</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,10 +3592,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -3621,7 +3615,7 @@
         <v>93</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3641,10 +3635,10 @@
         <v>93</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3661,10 +3655,10 @@
         <v>93</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,10 +3675,10 @@
         <v>93</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3701,10 +3695,10 @@
         <v>93</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3721,7 +3715,7 @@
         <v>93</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -3738,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -3761,7 +3755,7 @@
         <v>96</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -3781,10 +3775,10 @@
         <v>96</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,10 +3795,10 @@
         <v>96</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3821,7 +3815,7 @@
         <v>96</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>15</v>
@@ -3841,7 +3835,7 @@
         <v>96</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -3858,30 +3852,30 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -3898,13 +3892,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3918,13 +3912,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3938,10 +3932,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3958,10 +3952,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3978,13 +3972,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3998,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>15</v>
@@ -4018,32 +4012,12 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F137" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -319,13 +319,13 @@
     <t>10025006</t>
   </si>
   <si>
-    <t>NSTL KOKO COMBO 30 G</t>
+    <t>NESTLE KOKO.COMBO 30</t>
   </si>
   <si>
     <t>20032723</t>
   </si>
   <si>
-    <t>MILO CRL CKLT 30 G</t>
+    <t>MILO CEREAL COKLT 30</t>
   </si>
   <si>
     <t>20113150</t>
@@ -337,13 +337,13 @@
     <t>20111959</t>
   </si>
   <si>
-    <t>NSTL KOKO D CHO 30 G</t>
+    <t>KOKO KRNCH DB.CHO 30</t>
   </si>
   <si>
     <t>20046903</t>
   </si>
   <si>
-    <t>NSTL HONY STAR 30 G</t>
+    <t>NESTLE HONY STAR 30G</t>
   </si>
   <si>
     <t>20136090</t>
@@ -490,13 +490,13 @@
     <t>20036590</t>
   </si>
   <si>
-    <t>LWK WHKO ORG 9x20 G</t>
+    <t>LUWAK WHT ORGL 9X20</t>
   </si>
   <si>
     <t>20073043</t>
   </si>
   <si>
-    <t>LWK WHKO LS 9x19 G</t>
+    <t>LUWAK WHT LESS 9'S</t>
   </si>
   <si>
     <t>20055300</t>
@@ -805,7 +805,7 @@
     <t>10038932</t>
   </si>
   <si>
-    <t>KAPAPI S MIX 10x23 G</t>
+    <t>KPL API SPC MIX 10'S</t>
   </si>
   <si>
     <t>10003873</t>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
   <si>
     <t/>
   </si>
@@ -668,6 +668,12 @@
   </si>
   <si>
     <t>ENRGEN CKLT BOX 5'S</t>
+  </si>
+  <si>
+    <t>20143084</t>
+  </si>
+  <si>
+    <t>ENRGN TPNG BENG BL2S</t>
   </si>
   <si>
     <t>20131221</t>
@@ -1291,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3175,7 +3181,7 @@
         <v>58</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -3195,7 +3201,7 @@
         <v>58</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -3215,7 +3221,7 @@
         <v>58</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -3235,7 +3241,7 @@
         <v>58</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -3255,7 +3261,7 @@
         <v>58</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -3275,7 +3281,7 @@
         <v>58</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3292,13 +3298,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3315,7 +3321,7 @@
         <v>61</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>182</v>
@@ -3335,7 +3341,7 @@
         <v>61</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>182</v>
@@ -3355,10 +3361,10 @@
         <v>61</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>23</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3375,10 +3381,10 @@
         <v>61</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3395,7 +3401,7 @@
         <v>61</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3415,10 +3421,10 @@
         <v>61</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3432,10 +3438,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>15</v>
@@ -3455,10 +3461,10 @@
         <v>90</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,7 +3481,7 @@
         <v>90</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3495,10 +3501,10 @@
         <v>90</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3515,7 +3521,7 @@
         <v>90</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -3535,7 +3541,7 @@
         <v>90</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3555,10 +3561,10 @@
         <v>90</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3575,10 +3581,10 @@
         <v>90</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3592,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -3615,7 +3621,7 @@
         <v>93</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3635,10 +3641,10 @@
         <v>93</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3655,10 +3661,10 @@
         <v>93</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3675,10 +3681,10 @@
         <v>93</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3695,10 +3701,10 @@
         <v>93</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3715,7 +3721,7 @@
         <v>93</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>15</v>
@@ -3732,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>15</v>
@@ -3755,7 +3761,7 @@
         <v>96</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>15</v>
@@ -3775,10 +3781,10 @@
         <v>96</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3795,10 +3801,10 @@
         <v>96</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,7 +3821,7 @@
         <v>96</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>15</v>
@@ -3835,7 +3841,7 @@
         <v>96</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>15</v>
@@ -3852,30 +3858,30 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>96</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -3892,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3912,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3952,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3972,13 +3978,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3992,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>15</v>
@@ -4012,12 +4018,32 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E137" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F137" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="301">
   <si>
     <t/>
   </si>
@@ -94,9 +94,6 @@
     <t>7</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
     <t>20021935</t>
   </si>
   <si>
@@ -604,6 +601,12 @@
     <t>CHOCODRINK BLG 6'S</t>
   </si>
   <si>
+    <t>20143503</t>
+  </si>
+  <si>
+    <t>CHOCLTOS MTCHA 5'S</t>
+  </si>
+  <si>
     <t>20131214</t>
   </si>
   <si>
@@ -724,6 +727,12 @@
     <t>K/API KOPI SUSU10X31</t>
   </si>
   <si>
+    <t>20127276</t>
+  </si>
+  <si>
+    <t>LWK KOPI MURNI 9'S</t>
+  </si>
+  <si>
     <t>20046081</t>
   </si>
   <si>
@@ -850,15 +859,21 @@
     <t>K/API KOPI SPCL 150G</t>
   </si>
   <si>
+    <t>20143384</t>
+  </si>
+  <si>
+    <t>K/A BLCK COFE SPR10S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>20136451</t>
   </si>
   <si>
     <t>NSCAFE AMERICANO 10S</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>20142007</t>
   </si>
   <si>
@@ -899,12 +914,6 @@
   </si>
   <si>
     <t>KAPAL API SPECIAL 90</t>
-  </si>
-  <si>
-    <t>20127276</t>
-  </si>
-  <si>
-    <t>LWK KOPI MURNI 9'S</t>
   </si>
 </sst>
 </file>
@@ -1297,14 +1306,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,15 +1473,15 @@
         <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1481,7 +1490,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>19</v>
@@ -1489,10 +1498,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1509,10 +1518,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1529,10 +1538,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1549,10 +1558,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1569,10 +1578,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1589,10 +1598,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1609,10 +1618,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1641,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
@@ -1649,10 +1658,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1661,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>15</v>
@@ -1669,10 +1678,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1681,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1689,10 +1698,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1701,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1721,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>23</v>
@@ -1729,10 +1738,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1741,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -1749,10 +1758,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1769,10 +1778,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1789,10 +1798,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1809,10 +1818,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1829,10 +1838,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1849,10 +1858,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1869,10 +1878,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1889,10 +1898,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1901,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>15</v>
@@ -1909,10 +1918,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1921,7 +1930,7 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1929,10 +1938,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1941,7 +1950,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>15</v>
@@ -1949,10 +1958,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1961,7 +1970,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1969,10 +1978,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1981,7 +1990,7 @@
         <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>15</v>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2001,7 +2010,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>23</v>
@@ -2009,10 +2018,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2021,7 +2030,7 @@
         <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -2029,10 +2038,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2041,7 +2050,7 @@
         <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>19</v>
@@ -2049,10 +2058,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2061,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>23</v>
@@ -2069,10 +2078,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2089,10 +2098,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2109,10 +2118,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2129,10 +2138,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2149,10 +2158,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2169,10 +2178,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2189,10 +2198,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2209,10 +2218,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2221,7 +2230,7 @@
         <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>23</v>
@@ -2229,10 +2238,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2244,15 +2253,15 @@
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2264,15 +2273,15 @@
         <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2289,10 +2298,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2309,10 +2318,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2329,10 +2338,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2349,10 +2358,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2369,10 +2378,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2389,10 +2398,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2409,10 +2418,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2429,10 +2438,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2449,10 +2458,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2469,10 +2478,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2489,10 +2498,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2509,10 +2518,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2529,10 +2538,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2549,10 +2558,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -2569,10 +2578,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>149</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2589,10 +2598,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2601,7 +2610,7 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2609,10 +2618,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2621,7 +2630,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>19</v>
@@ -2629,10 +2638,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2641,18 +2650,18 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2661,7 +2670,7 @@
         <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>19</v>
@@ -2669,16 +2678,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>4</v>
@@ -2689,16 +2698,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -2709,16 +2718,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>11</v>
@@ -2729,16 +2738,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>4</v>
@@ -2749,16 +2758,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -2769,16 +2778,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>11</v>
@@ -2789,16 +2798,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>14</v>
@@ -2809,36 +2818,36 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>22</v>
@@ -2849,96 +2858,96 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>11</v>
@@ -2949,56 +2958,56 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>22</v>
@@ -3009,16 +3018,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>4</v>
@@ -3029,16 +3038,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -3049,16 +3058,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>11</v>
@@ -3069,16 +3078,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>14</v>
@@ -3089,16 +3098,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>18</v>
@@ -3109,59 +3118,59 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>23</v>
@@ -3169,19 +3178,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>23</v>
@@ -3189,19 +3198,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>23</v>
@@ -3209,19 +3218,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>23</v>
@@ -3229,19 +3238,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>23</v>
@@ -3249,19 +3258,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>23</v>
@@ -3269,19 +3278,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>23</v>
@@ -3289,19 +3298,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>23</v>
@@ -3309,179 +3318,179 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3489,39 +3498,39 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>23</v>
@@ -3529,19 +3538,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>23</v>
@@ -3549,19 +3558,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>23</v>
@@ -3569,39 +3578,39 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>23</v>
@@ -3609,19 +3618,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>23</v>
@@ -3629,19 +3638,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>23</v>
@@ -3649,59 +3658,59 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3709,99 +3718,99 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>23</v>
@@ -3809,79 +3818,79 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>23</v>
@@ -3889,19 +3898,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>23</v>
@@ -3909,39 +3918,39 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>23</v>
@@ -3949,19 +3958,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>23</v>
@@ -3969,82 +3978,122 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>5</v>
+      <c r="B138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -868,6 +868,12 @@
     <t>17</t>
   </si>
   <si>
+    <t>20017575</t>
+  </si>
+  <si>
+    <t>NESCAFE CLSC 10X2G</t>
+  </si>
+  <si>
     <t>20136451</t>
   </si>
   <si>
@@ -884,12 +890,6 @@
   </si>
   <si>
     <t>NESCAFE CLASSIC 100G</t>
-  </si>
-  <si>
-    <t>20017575</t>
-  </si>
-  <si>
-    <t>NESCAFE CLSC 10X2G</t>
   </si>
   <si>
     <t>10005302</t>
@@ -3993,7 +3993,7 @@
         <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>18</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">

--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -487,13 +487,13 @@
     <t>20036590</t>
   </si>
   <si>
-    <t>LUWAK WHT ORGL 9X20</t>
+    <t>LUWAK WHT ORG 9x20 G</t>
   </si>
   <si>
     <t>20073043</t>
   </si>
   <si>
-    <t>LUWAK WHT LESS 9'S</t>
+    <t>LUWAK WHT LS 9x19 G</t>
   </si>
   <si>
     <t>20055300</t>
@@ -541,7 +541,7 @@
     <t>20031318</t>
   </si>
   <si>
-    <t>G/DAY CPUCINO 10X25G</t>
+    <t>G/DAY CPCINO 10X25 G</t>
   </si>
   <si>
     <t>10003922</t>
@@ -796,7 +796,7 @@
     <t>20125856</t>
   </si>
   <si>
-    <t>LUWAK KOPI MRN 100G</t>
+    <t>LWK KOPI MURNI 100 G</t>
   </si>
   <si>
     <t>20055977</t>
@@ -820,7 +820,7 @@
     <t>10038932</t>
   </si>
   <si>
-    <t>KPL API SPC MIX 10'S</t>
+    <t>K/A SPC MIX 10x23 G</t>
   </si>
   <si>
     <t>10003873</t>
@@ -2350,7 +2350,7 @@
         <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>23</v>
